--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-09T09:28:26+00:00</t>
+    <t>2023-10-16T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:03:47+00:00</t>
+    <t>2023-10-16T13:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:05:21+00:00</t>
+    <t>2023-10-16T13:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-organization-uf-activity-field</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-organization-uf-activity-field</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:49:57+00:00</t>
+    <t>2023-10-23T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T09:15:45+00:00</t>
+    <t>2023-10-23T11:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T11:28:06+00:00</t>
+    <t>2023-11-06T10:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:15:36+00:00</t>
+    <t>2023-11-07T09:05:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from fr-v2-3311" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from FR Core CodeSyst" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T09:05:25+00:00</t>
+    <t>2023-11-08T15:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,7 +141,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://interopsante.org/fhir/CodeSystem/fr-v2-3311</t>
+    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-3311</t>
   </si>
 </sst>
 </file>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
   <si>
     <t>Property</t>
   </si>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T15:11:22+00:00</t>
+    <t>2023-11-21T10:12:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -334,66 +337,68 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -412,90 +417,90 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T10:12:39+00:00</t>
+    <t>2023-12-04T10:06:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T10:06:25+00:00</t>
+    <t>2023-12-04T12:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T12:30:51+00:00</t>
+    <t>2023-12-04T12:32:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="46">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T12:32:37+00:00</t>
+    <t>2023-12-11T10:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -73,6 +73,12 @@
   </si>
   <si>
     <t>No display for ContactDetail</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -278,7 +284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -385,20 +391,28 @@
       <c r="A13" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B15" t="s" s="2">
         <v>25</v>
+      </c>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -417,90 +431,90 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:19:21+00:00</t>
+    <t>2023-12-11T10:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:51:09+00:00</t>
+    <t>2023-12-11T13:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T13:13:22+00:00</t>
+    <t>2023-12-19T10:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:49:53+00:00</t>
+    <t>2023-12-22T08:30:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-22T08:30:59+00:00</t>
+    <t>2024-01-19T16:14:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:14:08+00:00</t>
+    <t>2024-01-22T11:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:15+00:00</t>
+    <t>2024-01-22T11:10:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:58+00:00</t>
+    <t>2024-01-29T10:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:14:55+00:00</t>
+    <t>2024-01-29T10:26:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
+++ b/ig/main/ValueSet-fr-core-organization-uf-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:26:27+00:00</t>
+    <t>2024-02-05T10:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
